--- a/output/2026-09-01_05_Italia_Umbria_Componentistica_Ventilazione_industriale.xlsx
+++ b/output/2026-09-01_05_Italia_Umbria_Componentistica_Ventilazione_industriale.xlsx
@@ -478,7 +478,6 @@
           <t>Braganti S.r.l.</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Perugia (PG)</t>
@@ -494,7 +493,6 @@
           <t>075 5289176</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Condotte in lamiera/poliuretano, ventilatori, canne fumarie, trattamento aria. Esistenza confermata (PagineBianche, Kompass, Europages, Facebook aziendale). Attiva dal 1985.</t>
@@ -581,7 +579,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Impianti di aspirazione/filtrazione aria, carpenteria metallica, nastri trasportatori. Attiva dal 1983 (ex Costruzioni Metalliche Massini &amp; C.).</t>
+          <t>Impianti di aspirazione/filtrazione aria, carpenteria metallica, nastri trasportatori. Attiva dal 1983 (ex Costruzioni Metalliche Massini &amp; C.). [DUPLICATO — vedi anche: 2026-09-01_03_Italia_Umbria_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -623,7 +621,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Impianti di aspirazione aria, filtrazione fumi/polveri, canne fumarie, ventilazione/climatizzazione industriale. Fondata nel 1982.</t>
+          <t>Impianti di aspirazione aria, filtrazione fumi/polveri, canne fumarie, ventilazione/climatizzazione industriale. Fondata nel 1982. [DUPLICATO — vedi anche: 2026-08-31_09_Italia_Toscana_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -658,7 +656,6 @@
           <t>0744 812969</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Motori elettrici, pompe, elettromeccanica industriale (componentistica affine, usata anche per ventilatori). ISO 9001, attiva da oltre 50 anni. Non specializzata in ventilazione pura.</t>
@@ -696,7 +693,6 @@
           <t>0744 800293 / 0744 800294</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Motori elettrici, trasformatori, riduttori/variatori, componenti elettrotecnici. Attività prevalente riparazione/manutenzione motori: affine ma non specifica per ventilazione.</t>
@@ -734,7 +730,6 @@
           <t>0744 814812 / 0744 815960</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Trasmissioni meccaniche, oleodinamica, pneumatica, cuscinetti. Fornitore generalista di componentistica meccanica, affine ma non specifico per ventilazione. Fondata nel 2006.</t>
